--- a/SchoolExamReports.xlsx
+++ b/SchoolExamReports.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17900" windowHeight="6800" tabRatio="817"/>
+    <workbookView windowWidth="17900" windowHeight="6800" tabRatio="817" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="116">
   <si>
     <t>ClICK HERE TO GO TO:</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Enter Your School Name Hereh➡️</t>
   </si>
   <si>
-    <t>KALPOHIN ANGLICAN PRIMARY</t>
+    <t>ANBARIYA SENIOR HIGH SCHOOL</t>
   </si>
   <si>
     <t>NAME</t>
@@ -70,13 +70,16 @@
     <t>ADAM FATI</t>
   </si>
   <si>
-    <t>INUSAH FATAW</t>
-  </si>
-  <si>
     <t>ALAHASSAN IDDRISU</t>
   </si>
   <si>
+    <t>ALHASSAN FATIMA</t>
+  </si>
+  <si>
     <t>BABA FUSEINI</t>
+  </si>
+  <si>
+    <t>INUSAH FATAW</t>
   </si>
   <si>
     <t>ENGLISH</t>
@@ -617,7 +620,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,12 +648,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1267,7 +1264,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1291,16 +1288,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1309,89 +1306,89 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1583,12 +1580,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="22" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="23" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1598,10 +1589,10 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="25" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="6" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
@@ -2148,7 +2139,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2470150" y="69850"/>
-          <a:ext cx="2190750" cy="5026660"/>
+          <a:ext cx="2190750" cy="5017135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2509,6 +2500,9 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:A62" totalsRowShown="0">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A62" etc:filterBottomFollowUsedRange="0"/>
+  <sortState ref="A2:A62">
+    <sortCondition ref="A1"/>
+  </sortState>
   <tableColumns count="1">
     <tableColumn id="1" name="NAME" dataDxfId="0"/>
   </tableColumns>
@@ -2999,39 +2993,39 @@
       <c r="A5" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="64"/>
     </row>
     <row r="6" ht="27.25" spans="1:9">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="70"/>
-      <c r="I6" s="74" t="str">
+      <c r="B6" s="67"/>
+      <c r="C6" s="68"/>
+      <c r="I6" s="72" t="str">
         <f>IF($I$4+H4=100%,"SUCCESS","Test Percentage and Continuous Assessment Percentage MUST sum to 100%. It should not be LESS or MORE")</f>
         <v>SUCCESS</v>
       </c>
     </row>
     <row r="7" ht="27.25" spans="1:3">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
     </row>
     <row r="8" ht="27.25" spans="1:3">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-    </row>
-    <row r="9" ht="15.25" spans="8:9">
-      <c r="H9" s="73" t="s">
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+    </row>
+    <row r="9" spans="8:9">
+      <c r="H9" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="73" t="s">
+      <c r="I9" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3083,7 +3077,7 @@
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="55" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3098,7 +3092,9 @@
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="55"/>
+      <c r="A6" s="56" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="56"/>
@@ -3297,55 +3293,55 @@
   <sheetData>
     <row r="4" spans="2:37">
       <c r="B4" s="51" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="51"/>
       <c r="D4" s="51"/>
       <c r="E4" s="51"/>
       <c r="F4" s="51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="51"/>
       <c r="H4" s="51"/>
       <c r="I4" s="51"/>
       <c r="J4" s="51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" s="51"/>
       <c r="L4" s="51"/>
       <c r="M4" s="51"/>
       <c r="N4" s="51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" s="51"/>
       <c r="P4" s="51"/>
       <c r="Q4" s="51"/>
       <c r="R4" s="51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S4" s="51"/>
       <c r="T4" s="51"/>
       <c r="U4" s="51"/>
       <c r="V4" s="51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W4" s="51"/>
       <c r="X4" s="51"/>
       <c r="Y4" s="51"/>
       <c r="Z4" s="51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA4" s="51"/>
       <c r="AB4" s="51"/>
       <c r="AC4" s="51"/>
       <c r="AD4" s="51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE4" s="51"/>
       <c r="AF4" s="51"/>
       <c r="AG4" s="51"/>
       <c r="AH4" s="51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI4" s="51"/>
       <c r="AJ4" s="51"/>
@@ -3356,112 +3352,112 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AD5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AE5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AF5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AG5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AH5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AI5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -3469,10 +3465,18 @@
         <f>'Students Names'!$A2</f>
         <v>ADAM FATI</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
+      <c r="B6" s="49">
+        <v>60</v>
+      </c>
+      <c r="C6" s="49">
+        <v>70</v>
+      </c>
+      <c r="D6" s="49">
+        <v>100</v>
+      </c>
+      <c r="E6" s="49">
+        <v>90</v>
+      </c>
       <c r="F6" s="49"/>
       <c r="G6" s="49"/>
       <c r="H6" s="49"/>
@@ -3509,7 +3513,7 @@
     <row r="7" spans="1:37">
       <c r="A7" s="53" t="str">
         <f>'Students Names'!$A3</f>
-        <v>INUSAH FATAW</v>
+        <v>ALAHASSAN IDDRISU</v>
       </c>
       <c r="B7" s="49"/>
       <c r="C7" s="49"/>
@@ -3551,7 +3555,7 @@
     <row r="8" spans="1:37">
       <c r="A8" s="52" t="str">
         <f>'Students Names'!$A4</f>
-        <v>ALAHASSAN IDDRISU</v>
+        <v>ALHASSAN FATIMA</v>
       </c>
       <c r="B8" s="49"/>
       <c r="C8" s="49"/>
@@ -3633,9 +3637,9 @@
       <c r="AK9" s="49"/>
     </row>
     <row r="10" spans="1:37">
-      <c r="A10" s="52">
+      <c r="A10" s="52" t="str">
         <f>'Students Names'!$A6</f>
-        <v>0</v>
+        <v>INUSAH FATAW</v>
       </c>
       <c r="B10" s="49"/>
       <c r="C10" s="49"/>
@@ -5553,37 +5557,40 @@
   <sheetPr/>
   <dimension ref="A1:J80"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="25.2727272727273" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="45" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="47" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5591,7 +5598,9 @@
         <f>'Students Names'!$A2</f>
         <v>ADAM FATI</v>
       </c>
-      <c r="B2" s="49"/>
+      <c r="B2" s="49">
+        <v>80</v>
+      </c>
       <c r="C2" s="49"/>
       <c r="D2" s="49"/>
       <c r="E2" s="49"/>
@@ -5604,7 +5613,7 @@
     <row r="3" spans="1:10">
       <c r="A3" s="48" t="str">
         <f>'Students Names'!$A3</f>
-        <v>INUSAH FATAW</v>
+        <v>ALAHASSAN IDDRISU</v>
       </c>
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
@@ -5619,7 +5628,7 @@
     <row r="4" spans="1:10">
       <c r="A4" s="48" t="str">
         <f>'Students Names'!$A4</f>
-        <v>ALAHASSAN IDDRISU</v>
+        <v>ALHASSAN FATIMA</v>
       </c>
       <c r="B4" s="49"/>
       <c r="C4" s="49"/>
@@ -5647,9 +5656,9 @@
       <c r="J5" s="49"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="48">
+      <c r="A6" s="48" t="str">
         <f>'Students Names'!$A6</f>
-        <v>0</v>
+        <v>INUSAH FATAW</v>
       </c>
       <c r="B6" s="49"/>
       <c r="C6" s="49"/>
@@ -6825,138 +6834,138 @@
   <sheetData>
     <row r="1" s="41" customFormat="1" spans="2:28">
       <c r="B1" s="42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="42"/>
       <c r="D1" s="42"/>
       <c r="E1" s="42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="42"/>
       <c r="G1" s="42"/>
       <c r="H1" s="42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I1" s="42"/>
       <c r="J1" s="42"/>
       <c r="K1" s="42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L1" s="42"/>
       <c r="M1" s="42"/>
       <c r="N1" s="42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O1" s="42"/>
       <c r="P1" s="42"/>
       <c r="Q1" s="42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R1" s="42"/>
       <c r="S1" s="42"/>
       <c r="T1" s="42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U1" s="42"/>
       <c r="V1" s="42"/>
       <c r="W1" s="42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X1" s="42"/>
       <c r="Y1" s="42"/>
       <c r="Z1" s="42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA1" s="42"/>
       <c r="AB1" s="42"/>
     </row>
     <row r="2" spans="1:29">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Z2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AB2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AC2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6964,17 +6973,17 @@
         <f>'Students Names'!$A2</f>
         <v>ADAM FATI</v>
       </c>
-      <c r="B3" s="43" t="str">
+      <c r="B3" s="43">
         <f>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!B6:E6)/COUNTA(ContinuousAssessment!B6:E6)),"")</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="C3" s="43">
         <f>Guide!$H$4*testResults!B2</f>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D3" s="43">
         <f>SUM(B3:C54)</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E3" s="43" t="str">
         <f>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!$F6:$I6)/COUNTA(ContinuousAssessment!$F6:$I6)),"")</f>
@@ -7074,13 +7083,13 @@
       </c>
       <c r="AC3" s="43">
         <f t="shared" ref="AC3:AC54" si="0">SUM(AB3,Y3,V3,S3,P3,M3,J3,G3,D3,)</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="43" t="str">
         <f>'Students Names'!$A3</f>
-        <v>INUSAH FATAW</v>
+        <v>ALAHASSAN IDDRISU</v>
       </c>
       <c r="B4" s="43" t="str">
         <f>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!B7:E7)/COUNTA(ContinuousAssessment!B7:E7)),"")</f>
@@ -7198,7 +7207,7 @@
     <row r="5" spans="1:29">
       <c r="A5" s="43" t="str">
         <f>'Students Names'!$A4</f>
-        <v>ALAHASSAN IDDRISU</v>
+        <v>ALHASSAN FATIMA</v>
       </c>
       <c r="B5" s="43" t="str">
         <f>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!B8:E8)/COUNTA(ContinuousAssessment!B8:E8)),"")</f>
@@ -7432,9 +7441,9 @@
       </c>
     </row>
     <row r="7" spans="1:29">
-      <c r="A7" s="43">
+      <c r="A7" s="43" t="str">
         <f>'Students Names'!$A6</f>
-        <v>0</v>
+        <v>INUSAH FATAW</v>
       </c>
       <c r="B7" s="43" t="str">
         <f>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!B10:E10)/COUNTA(ContinuousAssessment!B10:E10)),"")</f>
@@ -13145,7 +13154,7 @@
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="str">
         <f>Guide!$I$9</f>
-        <v>KALPOHIN ANGLICAN PRIMARY</v>
+        <v>ANBARIYA SENIOR HIGH SCHOOL</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -13158,10 +13167,10 @@
     <row r="4" ht="29" customHeight="1" spans="2:10">
       <c r="B4" s="4"/>
       <c r="C4" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -13173,10 +13182,10 @@
     <row r="5" ht="29" customHeight="1" spans="2:10">
       <c r="B5" s="4"/>
       <c r="C5" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
@@ -13188,7 +13197,7 @@
     <row r="6" ht="21" customHeight="1" spans="2:10">
       <c r="B6" s="4"/>
       <c r="C6" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="12"/>
@@ -13201,7 +13210,7 @@
     <row r="7" ht="24" customHeight="1" spans="2:10">
       <c r="B7" s="4"/>
       <c r="C7" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
@@ -13214,22 +13223,22 @@
     <row r="8" ht="16.25" spans="2:10">
       <c r="B8" s="4"/>
       <c r="C8" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I8" s="21"/>
       <c r="J8" s="36"/>
@@ -13237,19 +13246,19 @@
     <row r="9" ht="15.25" spans="2:10">
       <c r="B9" s="4"/>
       <c r="C9" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="19" t="str">
-        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!Z$3:Z$54)</f>
-        <v/>
+        <v>16</v>
+      </c>
+      <c r="D9" s="19">
+        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!B$3:B$54)</f>
+        <v>24</v>
       </c>
       <c r="E9" s="19">
         <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!C$3:C$54)</f>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F9" s="19">
         <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!D$3:D$54)</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G9" s="19">
         <f>RANK(_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!D$3:D$54),overAll!D$3:D$54)</f>
@@ -13257,7 +13266,7 @@
       </c>
       <c r="H9" s="20" t="str">
         <f t="shared" ref="H9:H17" si="0">IF(F9&gt;=80,"Excellent",IF(F9&gt;=70,"Very Good",IF(F9&gt;=60,"Good",IF(F9&gt;=45,"Credit",IF(F9&gt;=35,"Pass",IF(F9&lt;35,"Fail"))))))</f>
-        <v>Fail</v>
+        <v>Excellent</v>
       </c>
       <c r="I9" s="21"/>
       <c r="J9" s="36"/>
@@ -13265,10 +13274,10 @@
     <row r="10" ht="15.25" spans="2:10">
       <c r="B10" s="4"/>
       <c r="C10" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="19" t="str">
-        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!Z$3:Z$54)</f>
+        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!E$3:E$54)</f>
         <v/>
       </c>
       <c r="E10" s="19">
@@ -13293,10 +13302,10 @@
     <row r="11" ht="15.25" spans="2:10">
       <c r="B11" s="4"/>
       <c r="C11" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" s="19" t="str">
-        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!Z$3:Z$54)</f>
+        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!H$3:H$54)</f>
         <v/>
       </c>
       <c r="E11" s="19">
@@ -13321,10 +13330,10 @@
     <row r="12" ht="15.25" spans="2:10">
       <c r="B12" s="4"/>
       <c r="C12" s="18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="19" t="str">
-        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!Z$3:Z$54)</f>
+        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!K$3:K$54)</f>
         <v/>
       </c>
       <c r="E12" s="19">
@@ -13349,10 +13358,10 @@
     <row r="13" ht="15.25" spans="2:10">
       <c r="B13" s="4"/>
       <c r="C13" s="18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" s="19" t="str">
-        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!Z$3:Z$54)</f>
+        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!N$3:N$54)</f>
         <v/>
       </c>
       <c r="E13" s="19">
@@ -13377,10 +13386,10 @@
     <row r="14" ht="15.25" spans="2:10">
       <c r="B14" s="4"/>
       <c r="C14" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="19" t="str">
-        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!Z$3:Z$54)</f>
+        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!Q$3:Q$54)</f>
         <v/>
       </c>
       <c r="E14" s="19">
@@ -13405,10 +13414,10 @@
     <row r="15" ht="15.25" spans="2:10">
       <c r="B15" s="4"/>
       <c r="C15" s="18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="19" t="str">
-        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!Z$3:Z$54)</f>
+        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!T$3:T$54)</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -13433,10 +13442,10 @@
     <row r="16" ht="15.25" spans="2:10">
       <c r="B16" s="4"/>
       <c r="C16" s="18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="19" t="str">
-        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!Z$3:Z$54)</f>
+        <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!W$3:W$54)</f>
         <v/>
       </c>
       <c r="E16" s="19">
@@ -13458,10 +13467,10 @@
       <c r="I16" s="21"/>
       <c r="J16" s="36"/>
     </row>
-    <row r="17" ht="15.25" spans="2:10">
+    <row r="17" spans="2:10">
       <c r="B17" s="4"/>
       <c r="C17" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" s="19" t="str">
         <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!Z$3:Z$54)</f>
@@ -13522,23 +13531,23 @@
     <row r="21" spans="2:10">
       <c r="B21" s="4"/>
       <c r="C21" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" s="22">
         <v>55</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F21" s="24"/>
       <c r="G21" s="25">
         <v>70</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I21" s="27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J21" s="37"/>
     </row>
@@ -13556,22 +13565,22 @@
     <row r="23" ht="17" customHeight="1" spans="2:10">
       <c r="B23" s="4"/>
       <c r="C23" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I23" s="26"/>
       <c r="J23" s="38"/>
@@ -13579,10 +13588,10 @@
     <row r="24" ht="18" customHeight="1" spans="2:10">
       <c r="B24" s="4"/>
       <c r="C24" s="29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F24" s="31"/>
       <c r="G24" s="31"/>
@@ -13593,7 +13602,7 @@
     <row r="25" ht="19" customHeight="1" spans="2:10">
       <c r="B25" s="4"/>
       <c r="C25" s="28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="32"/>

--- a/SchoolExamReports.xlsx
+++ b/SchoolExamReports.xlsx
@@ -3,6 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="RtIEnbX19JliYzOjRLjP6Y5xGapljxSGJBAbdehCu4AQ7UQVzEeWfbC1zbKprq0jIUGW+geBmRk0GK152XEvqg==" workbookSaltValue="ybB9gylNgClxpKQQW9Lh0w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView windowWidth="17900" windowHeight="6800" tabRatio="817" activeTab="5"/>
   </bookViews>
@@ -58,10 +59,10 @@
     <t>Test Results</t>
   </si>
   <si>
-    <t>Enter Your School Name Hereh➡️</t>
+    <t>Enter Your School Name Here➡️</t>
   </si>
   <si>
-    <t>ANBARIYA SENIOR HIGH SCHOOL</t>
+    <t>KALPOHIN ANGLICAN PRIMARY B</t>
   </si>
   <si>
     <t>NAME</t>
@@ -1388,7 +1389,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1577,8 +1578,9 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="22" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="23" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1600,6 +1602,10 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1653,7 +1659,13 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="97">
+  <dxfs count="99">
+    <dxf>
+      <protection locked="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0"/>
+    </dxf>
     <dxf>
       <protection locked="0"/>
     </dxf>
@@ -2087,25 +2099,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="86"/>
-      <tableStyleElement type="headerRow" dxfId="85"/>
-      <tableStyleElement type="totalRow" dxfId="84"/>
-      <tableStyleElement type="firstColumn" dxfId="83"/>
-      <tableStyleElement type="lastColumn" dxfId="82"/>
-      <tableStyleElement type="firstRowStripe" dxfId="81"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="80"/>
+      <tableStyleElement type="wholeTable" dxfId="88"/>
+      <tableStyleElement type="headerRow" dxfId="87"/>
+      <tableStyleElement type="totalRow" dxfId="86"/>
+      <tableStyleElement type="firstColumn" dxfId="85"/>
+      <tableStyleElement type="lastColumn" dxfId="84"/>
+      <tableStyleElement type="firstRowStripe" dxfId="83"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="82"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="96"/>
-      <tableStyleElement type="totalRow" dxfId="95"/>
-      <tableStyleElement type="firstRowStripe" dxfId="94"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="93"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="92"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="91"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="90"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="89"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="88"/>
-      <tableStyleElement type="pageFieldValues" dxfId="87"/>
+      <tableStyleElement type="headerRow" dxfId="98"/>
+      <tableStyleElement type="totalRow" dxfId="97"/>
+      <tableStyleElement type="firstRowStripe" dxfId="96"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="95"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="94"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="93"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="92"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="91"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="90"/>
+      <tableStyleElement type="pageFieldValues" dxfId="89"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2139,7 +2151,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2470150" y="69850"/>
-          <a:ext cx="2190750" cy="5017135"/>
+          <a:ext cx="2190750" cy="5026660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2326,7 +2338,7 @@
               <a:latin typeface="Segoe UI Semibold" panose="020B0702040204020203" charset="0"/>
               <a:cs typeface="Segoe UI Semibold" panose="020B0702040204020203" charset="0"/>
             </a:rPr>
-            <a:t>Again, In this section, SELECT your  Exam conversion and Exam Conversion Percentages</a:t>
+            <a:t>Again, In this section, SELECT your  Test conversion and Assessment Conversion Percentages</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" altLang="en-GB" sz="1400">
             <a:solidFill>
@@ -2490,8 +2502,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="H3:I4" totalsRowShown="0">
   <tableColumns count="2">
-    <tableColumn id="1" name="Test Percentage"/>
-    <tableColumn id="2" name="Continuous Assessment Percentage"/>
+    <tableColumn id="1" name="Test Percentage" dataDxfId="0"/>
+    <tableColumn id="2" name="Continuous Assessment Percentage" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2504,7 +2516,7 @@
     <sortCondition ref="A1"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="1" name="NAME" dataDxfId="0"/>
+    <tableColumn id="1" name="NAME" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2514,45 +2526,45 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A5:AK54" totalsRowShown="0">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A5:AK54" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="37">
-    <tableColumn id="1" name="NAME" dataDxfId="1">
+    <tableColumn id="1" name="NAME" dataDxfId="3">
       <calculatedColumnFormula>'Students Names'!$A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="english test1" dataDxfId="2"/>
-    <tableColumn id="3" name="english test2" dataDxfId="3"/>
-    <tableColumn id="4" name="english test3" dataDxfId="4"/>
-    <tableColumn id="5" name="english test4" dataDxfId="5"/>
-    <tableColumn id="6" name="math test1" dataDxfId="6"/>
-    <tableColumn id="7" name="math test2" dataDxfId="7"/>
-    <tableColumn id="8" name="math test3" dataDxfId="8"/>
-    <tableColumn id="9" name="math test4" dataDxfId="9"/>
-    <tableColumn id="10" name="science test1" dataDxfId="10"/>
-    <tableColumn id="11" name="science test2" dataDxfId="11"/>
-    <tableColumn id="12" name="science test3" dataDxfId="12"/>
-    <tableColumn id="13" name="science test4" dataDxfId="13"/>
-    <tableColumn id="14" name="history test1" dataDxfId="14"/>
-    <tableColumn id="15" name="history test2" dataDxfId="15"/>
-    <tableColumn id="16" name="history test3" dataDxfId="16"/>
-    <tableColumn id="17" name="history test4" dataDxfId="17"/>
-    <tableColumn id="18" name="rme test1" dataDxfId="18"/>
-    <tableColumn id="19" name="rme test2" dataDxfId="19"/>
-    <tableColumn id="20" name="rme test3" dataDxfId="20"/>
-    <tableColumn id="21" name="rme test4" dataDxfId="21"/>
-    <tableColumn id="22" name="arts test1" dataDxfId="22"/>
-    <tableColumn id="23" name="arts test2" dataDxfId="23"/>
-    <tableColumn id="24" name="arts test3" dataDxfId="24"/>
-    <tableColumn id="25" name="arts test4" dataDxfId="25"/>
-    <tableColumn id="26" name="owop test1" dataDxfId="26"/>
-    <tableColumn id="27" name="owop test2" dataDxfId="27"/>
-    <tableColumn id="28" name="owop test3" dataDxfId="28"/>
-    <tableColumn id="29" name="owop test4" dataDxfId="29"/>
-    <tableColumn id="30" name="computing test1" dataDxfId="30"/>
-    <tableColumn id="31" name="computing test2" dataDxfId="31"/>
-    <tableColumn id="32" name="computing test3" dataDxfId="32"/>
-    <tableColumn id="33" name="computing test4" dataDxfId="33"/>
-    <tableColumn id="34" name="ghLanguage test1" dataDxfId="34"/>
-    <tableColumn id="35" name="ghLanguage test2" dataDxfId="35"/>
-    <tableColumn id="36" name="ghLanguage test3" dataDxfId="36"/>
-    <tableColumn id="37" name="ghLanguage test4" dataDxfId="37"/>
+    <tableColumn id="2" name="english test1" dataDxfId="4"/>
+    <tableColumn id="3" name="english test2" dataDxfId="5"/>
+    <tableColumn id="4" name="english test3" dataDxfId="6"/>
+    <tableColumn id="5" name="english test4" dataDxfId="7"/>
+    <tableColumn id="6" name="math test1" dataDxfId="8"/>
+    <tableColumn id="7" name="math test2" dataDxfId="9"/>
+    <tableColumn id="8" name="math test3" dataDxfId="10"/>
+    <tableColumn id="9" name="math test4" dataDxfId="11"/>
+    <tableColumn id="10" name="science test1" dataDxfId="12"/>
+    <tableColumn id="11" name="science test2" dataDxfId="13"/>
+    <tableColumn id="12" name="science test3" dataDxfId="14"/>
+    <tableColumn id="13" name="science test4" dataDxfId="15"/>
+    <tableColumn id="14" name="history test1" dataDxfId="16"/>
+    <tableColumn id="15" name="history test2" dataDxfId="17"/>
+    <tableColumn id="16" name="history test3" dataDxfId="18"/>
+    <tableColumn id="17" name="history test4" dataDxfId="19"/>
+    <tableColumn id="18" name="rme test1" dataDxfId="20"/>
+    <tableColumn id="19" name="rme test2" dataDxfId="21"/>
+    <tableColumn id="20" name="rme test3" dataDxfId="22"/>
+    <tableColumn id="21" name="rme test4" dataDxfId="23"/>
+    <tableColumn id="22" name="arts test1" dataDxfId="24"/>
+    <tableColumn id="23" name="arts test2" dataDxfId="25"/>
+    <tableColumn id="24" name="arts test3" dataDxfId="26"/>
+    <tableColumn id="25" name="arts test4" dataDxfId="27"/>
+    <tableColumn id="26" name="owop test1" dataDxfId="28"/>
+    <tableColumn id="27" name="owop test2" dataDxfId="29"/>
+    <tableColumn id="28" name="owop test3" dataDxfId="30"/>
+    <tableColumn id="29" name="owop test4" dataDxfId="31"/>
+    <tableColumn id="30" name="computing test1" dataDxfId="32"/>
+    <tableColumn id="31" name="computing test2" dataDxfId="33"/>
+    <tableColumn id="32" name="computing test3" dataDxfId="34"/>
+    <tableColumn id="33" name="computing test4" dataDxfId="35"/>
+    <tableColumn id="34" name="ghLanguage test1" dataDxfId="36"/>
+    <tableColumn id="35" name="ghLanguage test2" dataDxfId="37"/>
+    <tableColumn id="36" name="ghLanguage test3" dataDxfId="38"/>
+    <tableColumn id="37" name="ghLanguage test4" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2562,18 +2574,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:J80" totalsRowShown="0">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J80" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="NAME" dataDxfId="38">
+    <tableColumn id="1" name="NAME" dataDxfId="40">
       <calculatedColumnFormula>'Students Names'!$A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="ENGLISH" dataDxfId="39"/>
-    <tableColumn id="3" name="MATHEMATICS" dataDxfId="40"/>
-    <tableColumn id="4" name="SCIENCE" dataDxfId="41"/>
-    <tableColumn id="5" name="HISTORY" dataDxfId="42"/>
-    <tableColumn id="6" name="RME" dataDxfId="43"/>
-    <tableColumn id="7" name="CREATIVE ARTS" dataDxfId="44"/>
-    <tableColumn id="8" name="OWOP" dataDxfId="45"/>
-    <tableColumn id="9" name="COMPUTING" dataDxfId="46"/>
-    <tableColumn id="10" name="DAGBANI" dataDxfId="47"/>
+    <tableColumn id="2" name="ENGLISH" dataDxfId="41"/>
+    <tableColumn id="3" name="MATHEMATICS" dataDxfId="42"/>
+    <tableColumn id="4" name="SCIENCE" dataDxfId="43"/>
+    <tableColumn id="5" name="HISTORY" dataDxfId="44"/>
+    <tableColumn id="6" name="RME" dataDxfId="45"/>
+    <tableColumn id="7" name="CREATIVE ARTS" dataDxfId="46"/>
+    <tableColumn id="8" name="OWOP" dataDxfId="47"/>
+    <tableColumn id="9" name="COMPUTING" dataDxfId="48"/>
+    <tableColumn id="10" name="DAGBANI" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2583,91 +2595,91 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tboverall" displayName="tboverall" ref="A2:AC54" totalsRowShown="0">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:AC54" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="29">
-    <tableColumn id="1" name="name of student" dataDxfId="48">
+    <tableColumn id="1" name="name of student" dataDxfId="50">
       <calculatedColumnFormula>'Students Names'!$A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="englishCA" dataDxfId="49">
+    <tableColumn id="2" name="englishCA" dataDxfId="51">
       <calculatedColumnFormula>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!B6:E6)/COUNTA(ContinuousAssessment!B6:E6)),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="englishTest" dataDxfId="50">
+    <tableColumn id="3" name="englishTest" dataDxfId="52">
       <calculatedColumnFormula>Guide!$H$4*testResults!B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" name="englishTotal" dataDxfId="51">
+    <tableColumn id="4" name="englishTotal" dataDxfId="53">
       <calculatedColumnFormula>SUM(B3:C54)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" name="mathCA" dataDxfId="52">
+    <tableColumn id="5" name="mathCA" dataDxfId="54">
       <calculatedColumnFormula>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!$F6:$I6)/COUNTA(ContinuousAssessment!$F6:$I6)),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="mathTest" dataDxfId="53">
+    <tableColumn id="6" name="mathTest" dataDxfId="55">
       <calculatedColumnFormula>Guide!$H$4*testResults!C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="mathTotal" dataDxfId="54">
+    <tableColumn id="7" name="mathTotal" dataDxfId="56">
       <calculatedColumnFormula>SUM(E3:F54)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="scienceCA" dataDxfId="55">
+    <tableColumn id="8" name="scienceCA" dataDxfId="57">
       <calculatedColumnFormula>IFERROR(Guide!$I$4*SUM(ContinuousAssessment!$J6:$M6)/COUNTA(ContinuousAssessment!$J6:$M6),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" name="scienceTest" dataDxfId="56">
+    <tableColumn id="9" name="scienceTest" dataDxfId="58">
       <calculatedColumnFormula>Guide!$H$4*testResults!D2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" name="scienceTotal" dataDxfId="57">
+    <tableColumn id="10" name="scienceTotal" dataDxfId="59">
       <calculatedColumnFormula>SUM(H3:I54)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" name="historyCA" dataDxfId="58">
+    <tableColumn id="11" name="historyCA" dataDxfId="60">
       <calculatedColumnFormula>IFERROR(SUM(ContinuousAssessment!$N6:$Q6)/COUNTA(ContinuousAssessment!$N6:$Q6)*Guide!$I$4,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" name="historyTest" dataDxfId="59">
+    <tableColumn id="12" name="historyTest" dataDxfId="61">
       <calculatedColumnFormula>Guide!$H$4*testResults!$E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" name="historyTotal" dataDxfId="60">
+    <tableColumn id="13" name="historyTotal" dataDxfId="62">
       <calculatedColumnFormula>SUM(K3:L54)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" name="rmeCA" dataDxfId="61">
+    <tableColumn id="14" name="rmeCA" dataDxfId="63">
       <calculatedColumnFormula>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!$R6:$U6))/COUNTA(ContinuousAssessment!R6:U6),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="rmeTest" dataDxfId="62">
+    <tableColumn id="15" name="rmeTest" dataDxfId="64">
       <calculatedColumnFormula>Guide!$H$4*testResults!F2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" name="rmeTotal" dataDxfId="63">
+    <tableColumn id="16" name="rmeTotal" dataDxfId="65">
       <calculatedColumnFormula>SUM(N3:O54)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" name="creativeArtsCA" dataDxfId="64">
+    <tableColumn id="17" name="creativeArtsCA" dataDxfId="66">
       <calculatedColumnFormula>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!$V6:$Y6)/COUNTA(ContinuousAssessment!$V6:$Y6)),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" name="creativeArtsTest" dataDxfId="65">
+    <tableColumn id="18" name="creativeArtsTest" dataDxfId="67">
       <calculatedColumnFormula>Guide!$H$4*testResults!G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" name="creativeArtsTotal" dataDxfId="66">
+    <tableColumn id="19" name="creativeArtsTotal" dataDxfId="68">
       <calculatedColumnFormula>SUM(Q3:R54)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="owopCA" dataDxfId="67">
+    <tableColumn id="20" name="owopCA" dataDxfId="69">
       <calculatedColumnFormula>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!$Z6:$AC6))/COUNTA(ContinuousAssessment!$Z6:$AC6),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" name="owopTest" dataDxfId="68">
+    <tableColumn id="21" name="owopTest" dataDxfId="70">
       <calculatedColumnFormula>Guide!$H$4*testResults!H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" name="owopTotal" dataDxfId="69">
+    <tableColumn id="22" name="owopTotal" dataDxfId="71">
       <calculatedColumnFormula>SUM(T3:U54)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" name="computingCA" dataDxfId="70">
+    <tableColumn id="23" name="computingCA" dataDxfId="72">
       <calculatedColumnFormula>IFERROR(((SUM(ContinuousAssessment!$AD6:$AF6))/COUNTA(ContinuousAssessment!$AD6:$AF6))*Guide!$I$4,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" name="computingTest" dataDxfId="71">
+    <tableColumn id="24" name="computingTest" dataDxfId="73">
       <calculatedColumnFormula>Guide!$H$4*testResults!I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" name="computingTotal" dataDxfId="72">
+    <tableColumn id="25" name="computingTotal" dataDxfId="74">
       <calculatedColumnFormula>SUM(W3:X54)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" name="GHLanguageCA" dataDxfId="73">
+    <tableColumn id="26" name="GHLanguageCA" dataDxfId="75">
       <calculatedColumnFormula>IFERROR((SUM(ContinuousAssessment!$AH6:$AK6)/COUNTA(ContinuousAssessment!AH6:AK6))*Guide!$I$4,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" name="GHLanguageTest" dataDxfId="74">
+    <tableColumn id="27" name="GHLanguageTest" dataDxfId="76">
       <calculatedColumnFormula>testResults!J2*Guide!$H$4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" name="GHLanguageTotal" dataDxfId="75">
+    <tableColumn id="28" name="GHLanguageTotal" dataDxfId="77">
       <calculatedColumnFormula>SUM(Z3:AA54)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" name="Overal Marks" dataDxfId="76">
+    <tableColumn id="29" name="Overal Marks" dataDxfId="78">
       <calculatedColumnFormula>SUM(AB3,Y3,V3,S3,P3,M3,J3,G3,D3,)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2679,15 +2691,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table11" displayName="Table11" ref="C8:H17" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" name="SUBJECT"/>
-    <tableColumn id="2" name="CLASS SCORE" dataDxfId="77">
+    <tableColumn id="2" name="CLASS SCORE" dataDxfId="79">
       <calculatedColumnFormula>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!Z$3:Z$54)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" name="EXAM SCORE"/>
     <tableColumn id="4" name="TOTAL SCORE"/>
-    <tableColumn id="5" name="POSITION" dataDxfId="78">
+    <tableColumn id="5" name="POSITION" dataDxfId="80">
       <calculatedColumnFormula>RANK(_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!H$3:H$54),overAll!$M$3:$M$54)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="REMARKS" dataDxfId="79">
+    <tableColumn id="6" name="REMARKS" dataDxfId="81">
       <calculatedColumnFormula>IF(F9&gt;=80,"Excellent",IF(F9&gt;=70,"Very Good",IF(F9&gt;=60,"Good",IF(F9&gt;=45,"Credit",IF(F9&gt;=35,"Pass",IF(F9&lt;35,"Fail"))))))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3021,15 +3033,16 @@
       <c r="B8" s="70"/>
       <c r="C8" s="70"/>
     </row>
-    <row r="9" spans="8:9">
+    <row r="9" ht="15.25" spans="8:9">
       <c r="H9" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="71" t="s">
+      <c r="I9" s="73" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="4">
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A4:C4"/>
@@ -5527,6 +5540,7 @@
       <c r="AK54" s="49"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="P3nxhnEIMt4at6gnJ64FTZT8dn69IO5Hp19Tf13PzAvKub5XAHkJiqB7Wm98IweURr1TIThNgRsN5noqthVCAQ==" saltValue="26OiAzU+ruC7C/coU9j8dg==" spinCount="100000" sheet="1" objects="1"/>
   <mergeCells count="9">
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="F4:I4"/>
@@ -5615,8 +5629,12 @@
         <f>'Students Names'!$A3</f>
         <v>ALAHASSAN IDDRISU</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
+      <c r="B3" s="49">
+        <v>88</v>
+      </c>
+      <c r="C3" s="49">
+        <v>0</v>
+      </c>
       <c r="D3" s="49"/>
       <c r="E3" s="49"/>
       <c r="F3" s="49"/>
@@ -6781,6 +6799,7 @@
       <c r="J80" s="49"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="1R1fDAm1Mn+pwZ9I1lcktD7Pwn9Hx+9/ye13sQjN/+/KqGbd0GkZzMFzOPbEhx/dhJBbZjegUxNMXOB65mkUCA==" saltValue="fReqp3xjRusKOgKEUHJLlQ==" spinCount="100000" sheet="1" objects="1"/>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Enter a VALID Exam&#10; Score. The score should&#10; not be LESS than 0 and&#10; NOT MORE than 100&#10;" sqref="A2:A80"/>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Enter a VALID Exam&#10; Score. The score should&#10; not be LESS than 0 and&#10; NOT MORE than 100&#10;" sqref="B2:J80">
@@ -6983,7 +7002,7 @@
       </c>
       <c r="D3" s="43">
         <f>SUM(B3:C54)</f>
-        <v>80</v>
+        <v>141.6</v>
       </c>
       <c r="E3" s="43" t="str">
         <f>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!$F6:$I6)/COUNTA(ContinuousAssessment!$F6:$I6)),"")</f>
@@ -7083,7 +7102,7 @@
       </c>
       <c r="AC3" s="43">
         <f t="shared" ref="AC3:AC54" si="0">SUM(AB3,Y3,V3,S3,P3,M3,J3,G3,D3,)</f>
-        <v>80</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -7097,11 +7116,11 @@
       </c>
       <c r="C4" s="43">
         <f>Guide!$H$4*testResults!B3</f>
-        <v>0</v>
+        <v>61.6</v>
       </c>
       <c r="D4" s="43">
         <f>SUM(B4:C5)</f>
-        <v>0</v>
+        <v>61.6</v>
       </c>
       <c r="E4" s="43" t="str">
         <f>IFERROR(Guide!$I$4*(SUM(ContinuousAssessment!$F7:$I7)/COUNTA(ContinuousAssessment!$F7:$I7)),"")</f>
@@ -7201,7 +7220,7 @@
       </c>
       <c r="AC4" s="43">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -8071,10 +8090,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K12" s="43" t="str">
-        <f>IFERROR(SUM(ContinuousAssessment!$N15:$Q15)/COUNTA(ContinuousAssessment!$N15:$Q15)*Guide!$I$4,"")</f>
-        <v/>
-      </c>
+      <c r="K12" s="43"/>
       <c r="L12" s="44">
         <f>Guide!$H$4*testResults!$E11</f>
         <v>0</v>
@@ -13105,6 +13121,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="9">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
@@ -13153,8 +13170,8 @@
     <row r="3" ht="24.25" spans="2:10">
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="str">
-        <f>Guide!$I$9</f>
-        <v>ANBARIYA SENIOR HIGH SCHOOL</v>
+        <f>UPPER(Guide!$I$9)</f>
+        <v>KALPOHIN ANGLICAN PRIMARY B</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -13170,7 +13187,7 @@
         <v>93</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -13248,25 +13265,25 @@
       <c r="C9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="19" t="str">
         <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!B$3:B$54)</f>
-        <v>24</v>
+        <v/>
       </c>
       <c r="E9" s="19">
         <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!C$3:C$54)</f>
-        <v>56</v>
+        <v>61.6</v>
       </c>
       <c r="F9" s="19">
         <f>_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!D$3:D$54)</f>
-        <v>80</v>
+        <v>61.6</v>
       </c>
       <c r="G9" s="19">
         <f>RANK(_xlfn.XLOOKUP($D$4,overAll!$A$3:$A$54,overAll!D$3:D$54),overAll!D$3:D$54)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="20" t="str">
         <f t="shared" ref="H9:H17" si="0">IF(F9&gt;=80,"Excellent",IF(F9&gt;=70,"Very Good",IF(F9&gt;=60,"Good",IF(F9&gt;=45,"Credit",IF(F9&gt;=35,"Pass",IF(F9&lt;35,"Fail"))))))</f>
-        <v>Excellent</v>
+        <v>Good</v>
       </c>
       <c r="I9" s="21"/>
       <c r="J9" s="36"/>
@@ -13625,6 +13642,7 @@
     </row>
     <row r="27" ht="15.25"/>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="eg4AJ0tGQbmiaC08xoqK5hf3ajRwEtpR6XMg11byCtKIN7elYfRynmfr8vtWM7uIIEV+V/JJJnM5GhVaNdhG/w==" saltValue="IXiz3neYUzHEl+DXfqsE+Q==" spinCount="100000" sheet="1" sort="0" objects="1"/>
   <mergeCells count="1">
     <mergeCell ref="D4:H4"/>
   </mergeCells>
@@ -13658,4 +13676,24 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
+  <rangeList sheetStid="2" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="6" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="3" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="5" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="1" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="4" master="" otherUserPermission="visible"/>
+</allowEditUser>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>